--- a/app/public/modelos/modelo-quantidade.xlsx
+++ b/app/public/modelos/modelo-quantidade.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Funcionarios" sheetId="1" r:id="rId1"/>
+    <sheet name="Dados" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,13 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D8"/>
-  <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
-    <col min="3" max="3" width="12.83203125" customWidth="1"/>
-    <col min="4" max="4" width="12.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -418,6 +412,9 @@
       <c r="D1" t="str">
         <v>QUANTIDADE</v>
       </c>
+      <c r="E1" t="str">
+        <v>CARGO_CONFIANCA</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -432,6 +429,9 @@
       <c r="D2">
         <v>12</v>
       </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -446,6 +446,9 @@
       <c r="D3">
         <v>8</v>
       </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -460,6 +463,9 @@
       <c r="D4">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -474,6 +480,9 @@
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -488,6 +497,9 @@
       <c r="D6">
         <v>1</v>
       </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -502,6 +514,9 @@
       <c r="D7">
         <v>6</v>
       </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -516,10 +531,13 @@
       <c r="D8">
         <v>2</v>
       </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/public/modelos/modelo-quantidade.xlsx
+++ b/app/public/modelos/modelo-quantidade.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +427,7 @@
         <v>CLT</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -472,10 +472,10 @@
         <v>11.111.111/0001-11</v>
       </c>
       <c r="B5" t="str">
-        <v>411010</v>
+        <v>411005</v>
       </c>
       <c r="C5" t="str">
-        <v>PCD</v>
+        <v>APRENDIZ</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -486,16 +486,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>11.111.111/0001-11</v>
+        <v>11.111.111/0002-22</v>
       </c>
       <c r="B6" t="str">
-        <v>411005</v>
+        <v>411010</v>
       </c>
       <c r="C6" t="str">
-        <v>APRENDIZ</v>
+        <v>CLT</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -506,38 +506,21 @@
         <v>11.111.111/0002-22</v>
       </c>
       <c r="B7" t="str">
-        <v>411010</v>
+        <v>351305</v>
       </c>
       <c r="C7" t="str">
-        <v>CLT</v>
+        <v>ESTAGIARIO</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>11.111.111/0002-22</v>
-      </c>
-      <c r="B8" t="str">
-        <v>351305</v>
-      </c>
-      <c r="C8" t="str">
-        <v>ESTAGIARIO</v>
-      </c>
-      <c r="D8">
-        <v>2</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/public/modelos/modelo-quantidade.xlsx
+++ b/app/public/modelos/modelo-quantidade.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:D10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,9 +412,6 @@
       <c r="D1" t="str">
         <v>QUANTIDADE</v>
       </c>
-      <c r="E1" t="str">
-        <v>CARGO_CONFIANCA</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -429,9 +426,6 @@
       <c r="D2">
         <v>13</v>
       </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -446,9 +440,6 @@
       <c r="D3">
         <v>8</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -463,9 +454,6 @@
       <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -480,47 +468,80 @@
       <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>11.111.111/0002-22</v>
+        <v>11.111.111/0001-11</v>
       </c>
       <c r="B6" t="str">
-        <v>411010</v>
+        <v>514320</v>
       </c>
       <c r="C6" t="str">
-        <v>CLT</v>
+        <v>AFASTADO PELO INSS</v>
       </c>
       <c r="D6">
-        <v>6</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>11.111.111/0002-22</v>
+        <v>11.111.111/0001-11</v>
       </c>
       <c r="B7" t="str">
-        <v>351305</v>
+        <v>514320</v>
       </c>
       <c r="C7" t="str">
-        <v>ESTAGIARIO</v>
+        <v>TERCEIRIZADO</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
-      <c r="E7">
-        <v>0</v>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>11.111.111/0002-22</v>
+      </c>
+      <c r="B8" t="str">
+        <v>411010</v>
+      </c>
+      <c r="C8" t="str">
+        <v>CLT</v>
+      </c>
+      <c r="D8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>11.111.111/0002-22</v>
+      </c>
+      <c r="B9" t="str">
+        <v>351305</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ESTAGIARIO</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>11.111.111/0002-22</v>
+      </c>
+      <c r="B10" t="str">
+        <v>411010</v>
+      </c>
+      <c r="C10" t="str">
+        <v>TRABALHO TEMPORARIO</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
   </ignoredErrors>
 </worksheet>
 </file>